--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45534</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>45909</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>46010</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>46162</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>46162</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44943</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45834</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45758</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45908</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45908</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>46177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45894</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45904</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45588</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45534</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45534</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>46199</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>45602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44496</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45807</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45849</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>44658</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>44717</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44809</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>45581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>45581</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44970</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>45709</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45442</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>46176</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>46142</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>46231</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45805</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45859</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45394</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>44582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44718</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44717</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44466</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44788</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44466</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44470</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44603</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44964</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45561</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44890</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45231</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45575</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45622</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45643</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45518</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45677</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45691</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44960</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45622</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45715</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45463</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44834</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45371</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>45244</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45702</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45443</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>45460</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44886</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45429</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45469</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45363</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45588</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44543</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45005</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45771</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>45372</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45075</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45463</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45428</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44964</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45251</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45807</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45086</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45671</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45890</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45463</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45133</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45807</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44546</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45904</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45554</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46140</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45831</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45820</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45911</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44993</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>44502</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44648</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45909</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45818</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45440</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45070</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44595</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45315</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44601</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45308</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45321</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44830</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45463</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45936</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>46148</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45940</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>44547</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>46048</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45594</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46148</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>46148</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>46148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>46148</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46148</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46148</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45946</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45947</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46048</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45947</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>46148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45951</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45951</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45471</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45471</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45949</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>46153</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44469</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44950</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45957</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45379</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45958</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45218</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45460</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44910</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45964</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45967</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45631</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44575</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>44797</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45513</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45498</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45933</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45308</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>46157</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45588</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44823</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>44820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45992</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45993</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45379</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46160</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46160</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>46162</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>46163</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45513</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46162</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45994</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45994</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45709</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>46163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45996</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45999</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45999</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46164</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>46167</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45999</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45999</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46167</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>46001</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>46167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45639</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>46002</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45622</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45950</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>46167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45181</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>46168</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45807</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46009</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>46168</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>46009</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>46013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>46013</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>46013</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45693</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44899</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45709</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>46168</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45540</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45281</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45154</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45643</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45562</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45429</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>46029</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>46029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>46029</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>46170</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45622</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45463</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44546</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45747</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45944</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45548</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>46042</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>46042</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45712</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45513</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>46048</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45009</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>46175</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>46055</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45548</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45604</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46177</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44938</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>46059</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46059</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46177</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>46178</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45189</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46181</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>46181</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>46076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46076</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46183</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>46080</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45818</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>46084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>46084</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>46084</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46084</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46183</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46187</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46087</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>46087</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45518</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45747</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45699</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>46093</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45334</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45621</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>46195</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>46196</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>46104</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45699</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44966</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>46105</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45321</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46198</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45107</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46112</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44543</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46199</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>46113</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45404</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>46120</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>46120</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45436</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>46121</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>46244</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45667</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45401</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>46127</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>46127</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>46133</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>46132</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>46133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>46246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>46134</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>44659</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>46247</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45223</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45603</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45693</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46206</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>46205</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45315</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45621</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>46205</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>46205</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46207</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46207</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45744</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>46207</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>46206</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>46206</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>46206</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>46162</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45631</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45771</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45268</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45208</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45548</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>46190</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>46252</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45169</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>46254</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45153</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45611</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>45107</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>46254</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46258</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45429</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45593</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45692</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46260</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>46260</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>46260</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>46260</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45641</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>46266</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45693</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46267</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46266</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46269</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>46225</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>46272</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>46230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45785</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>46029</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46278</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>46281</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>46281</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>46280</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>46238</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46281</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45793</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45793</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45793</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45796</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45796</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45323</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45803</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>45377</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45811</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45811</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45810</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45813</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45813</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45813</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45813</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45813</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45813</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45819</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45819</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45821</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45821</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45820</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>45820</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45820</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45820</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45825</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45824</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45824</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45824</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45824</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45826</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>45826</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45831</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45835</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45834</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45834</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45835</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45838</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45837</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45839</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45838</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45837</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45837</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>45840</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45840</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45845</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45869</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45869</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45870</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>45870</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45873</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45882</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45882</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>45882</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45882</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44741</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45485</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>45482</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45607</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45756</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45800</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45909</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>46162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44943</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45211</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45834</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>46177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45807</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45602</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>46195</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46199</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>45154</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46262</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>46226</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44496</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44658</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45442</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44717</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44809</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>46142</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>46176</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>46231</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45709</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44970</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45581</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45581</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45394</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44718</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44717</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44466</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44788</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44466</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44470</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45709</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45238</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45231</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45372</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45429</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45379</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45443</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45463</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44886</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45107</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45075</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45793</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45463</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45086</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46013</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45244</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45796</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45793</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45793</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>46029</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45428</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45807</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45377</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>46042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45807</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45712</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>44899</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45436</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45460</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46048</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45904</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45323</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45820</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>46055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>45803</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45518</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45518</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>46059</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45922</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>45513</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>46076</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44966</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45818</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>46080</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>46080</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>46084</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45810</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>46084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46084</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46084</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>46087</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46087</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45371</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45940</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45548</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45811</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45429</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45401</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46104</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45947</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>46105</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45949</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45951</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45107</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45954</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46113</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>46112</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45957</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45076</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46121</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45744</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>46120</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45964</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>46120</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45622</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45967</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45813</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45813</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45813</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45813</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45813</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>46127</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46127</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45643</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45631</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44993</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>46132</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46133</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45575</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45604</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45611</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>46133</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>46134</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45699</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45986</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45988</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45992</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45699</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44820</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>44823</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45993</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45996</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45999</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45909</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45440</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45999</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>46001</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>46002</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45643</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45807</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45208</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45820</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45820</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45819</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46009</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45671</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45820</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46013</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45821</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45821</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44659</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45824</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45818</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45824</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45824</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45826</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44648</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>45826</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45747</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45825</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22724,7 +22724,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45831</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46148</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>46148</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>46148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46148</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46148</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46148</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44469</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>44890</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46153</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45834</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45933</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45315</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45834</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45838</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45835</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45562</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45837</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46160</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45838</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45835</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46160</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45837</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>46162</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45837</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>46162</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>46162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45839</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45840</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45840</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44966</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>45845</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46164</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45818</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>46167</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>46167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>46167</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>46167</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46168</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46167</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45189</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>46170</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45944</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45379</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>44964</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>46177</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45469</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46177</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45869</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45870</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45870</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45404</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45869</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46178</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45460</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>46181</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>46181</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>46183</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45429</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>46183</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46183</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45009</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46187</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45873</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45133</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45771</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45588</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45540</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45070</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45141</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44543</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46195</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44595</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46196</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45513</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45622</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46198</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46198</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>46199</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45882</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45882</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45882</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45321</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>46205</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>46205</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45677</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>46207</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46207</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46206</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>46206</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>46206</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>45189</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>46206</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45097</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>46207</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>46252</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46254</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>46190</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>46254</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>46253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>46162</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45622</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45622</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>46254</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46254</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45715</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45621</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45561</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45709</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>46258</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45693</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46260</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>46260</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45702</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45251</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45463</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45693</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45641</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45181</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>46260</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>46266</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>46225</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46267</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46272</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46269</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45092</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46230</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46029</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>44575</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45693</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45631</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45548</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>46280</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>46278</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>44543</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>46281</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46281</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45471</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45471</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>46238</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45463</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44880</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>46093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44830</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>46288</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>46244</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>46287</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>44960</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46287</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>46244</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45890</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46247</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45169</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45308</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45308</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46290</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46048</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45363</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45603</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44834</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>46246</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>46288</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45498</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>44930</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>44502</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45005</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45153</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45639</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>44601</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45594</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44973</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45154</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45692</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45513</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>44910</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45160</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45621</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45218</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45223</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45180</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>45315</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45321</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45610</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45667</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45463</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44964</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45554</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45548</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45782</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45785</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44741</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45485</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45482</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45607</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45756</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45800</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46030</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45909</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>46162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44943</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45211</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45834</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>46177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>46258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45807</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45602</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>46195</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46199</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>45154</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46262</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>46226</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44496</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44658</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45442</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44717</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44809</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>46142</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>46176</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>46231</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45709</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44970</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45581</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45581</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45394</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44718</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44717</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44466</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44788</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44466</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44470</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45709</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45238</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45231</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45372</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45429</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45379</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45443</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45463</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44886</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45107</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45075</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45793</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45463</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45086</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46013</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45244</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45796</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45793</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45793</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>46029</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45428</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45807</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45377</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>46042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45807</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45712</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>44899</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45436</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45460</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46048</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45904</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45323</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45820</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>46055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>45803</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45518</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45518</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>46059</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45922</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>45513</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>46076</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44966</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45818</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>46080</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>46080</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>46084</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45810</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>46084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46084</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46084</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>46087</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46087</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45371</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45940</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45548</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45811</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45429</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45401</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46104</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45947</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>46105</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45949</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45951</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45107</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45954</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46113</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>46112</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45957</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45076</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46121</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45744</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>46120</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45964</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>46120</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45622</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45967</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45813</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45813</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45813</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45813</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45813</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>46127</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46127</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45643</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45631</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44993</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>46132</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46133</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45575</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45604</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45611</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>46133</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>46134</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45699</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45986</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45988</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45992</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45699</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44820</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>44823</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45993</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45996</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45999</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45909</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45440</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45999</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>46001</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>46002</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45643</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45807</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45208</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45820</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45820</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45819</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46009</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45671</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45820</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46013</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45821</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45821</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44659</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45824</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45818</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45824</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45824</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45826</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44648</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>45826</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45747</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45825</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22724,7 +22724,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45831</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46148</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>46148</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>46148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46148</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46148</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46148</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44469</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>44890</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46153</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45834</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45933</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45315</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45834</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45838</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45835</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45562</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45837</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46160</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45838</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45835</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46160</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45837</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>46162</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45837</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>46162</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>46162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45839</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45840</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45840</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44966</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>45845</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46164</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45818</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>46167</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>46167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>46167</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>46167</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46168</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46167</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45189</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>46170</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45944</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45379</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>44964</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>46177</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45469</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46177</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45869</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45870</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45870</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45404</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45869</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46178</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45460</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>46181</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>46181</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>46183</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45429</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>46183</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46183</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45009</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46187</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45873</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45133</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45771</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45588</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45540</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45070</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45141</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44543</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46195</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44595</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46196</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45513</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45622</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46198</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46198</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>46199</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45882</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45882</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45882</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45321</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>46205</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>46205</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45677</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>46207</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46207</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46206</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>46206</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>46206</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>45189</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>46206</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45097</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>46207</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>46252</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46254</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>46190</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>46254</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>46253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>46162</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45622</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45622</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>46254</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46254</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45715</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45621</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45561</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45709</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>46258</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45693</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46260</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>46260</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45702</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45251</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45463</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45693</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45641</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45181</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>46260</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>46266</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>46225</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46267</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46272</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46269</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45092</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46230</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46029</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>44575</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45693</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45631</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45548</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>46280</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>46278</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>44543</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>46281</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46281</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45471</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45471</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>46238</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45463</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44880</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>46093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44830</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>46288</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>46244</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>46287</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>44960</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46287</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>46244</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45890</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46247</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45169</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45308</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45308</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46290</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46048</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45363</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45603</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44834</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>46246</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>46288</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45498</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>44930</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>44502</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45005</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45153</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45639</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>44601</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45594</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44973</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45154</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45692</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45513</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>44910</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45160</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45621</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45218</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45223</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45180</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>45315</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45321</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45610</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45667</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45463</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44964</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45554</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45548</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45782</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45785</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44741</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45485</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45482</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45607</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45756</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45800</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46030</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>46162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45211</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45834</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>46290</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45758</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45769</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>46177</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>46258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46009</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45807</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45170</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44966</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45588</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>46195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>46199</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45154</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45534</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45534</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>45602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>44658</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44717</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>44809</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>45581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44539</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45709</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>46187</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46142</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>46231</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45442</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44582</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44550</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44718</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44717</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44755</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44788</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44875</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44510</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44530</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44698</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44501</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44880</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45231</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45622</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44603</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44964</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45561</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44890</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45231</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45643</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44960</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45807</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>46009</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>46009</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45518</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45677</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>46013</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>46013</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45807</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>45715</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45463</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46029</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45807</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45793</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45793</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45793</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45371</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45909</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45820</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>46042</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45712</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>46048</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45323</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45377</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45811</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45443</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45460</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45702</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>46059</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45936</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45469</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45429</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45940</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45811</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45588</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45810</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>46076</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45180</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45947</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45363</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>46080</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46080</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45951</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45951</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45818</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45949</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>46084</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>46084</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>46084</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44543</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>46084</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>46084</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>46084</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45813</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45957</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45954</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45813</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45958</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46087</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>46087</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45813</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45813</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45097</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45005</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45372</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45964</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45771</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45075</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45463</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44930</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>46104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45141</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45819</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>46105</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45981</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45821</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45821</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45820</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45820</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>46112</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45820</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>46113</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45986</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45824</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45824</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45824</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44823</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45824</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>46120</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45988</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46120</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45992</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45826</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46121</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45428</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45238</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45826</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45996</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45999</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45999</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45999</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46001</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>46127</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>46127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46133</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>46132</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45251</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45831</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45671</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45835</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45189</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45834</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45834</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44659</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45835</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45189</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45838</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45837</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>45133</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45839</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45838</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45837</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45837</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45840</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45840</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44546</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45554</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44993</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>44502</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44595</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45315</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>44601</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45092</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45308</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>46139</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45321</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44830</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45463</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46140</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44648</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45909</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45818</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45869</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45440</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45594</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45869</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45471</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45471</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45870</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45870</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45873</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44950</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46148</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45379</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46148</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>46148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>46148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>46148</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>46148</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46148</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>46148</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45218</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45460</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44910</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45933</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45631</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44575</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46160</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46162</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46162</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>46163</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46164</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>46167</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46167</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45818</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45513</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46167</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45498</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45950</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>46167</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46167</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45308</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46168</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46170</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45882</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>44973</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45588</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45882</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45379</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45882</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45086</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>46177</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>46181</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46181</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45513</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>46183</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>46183</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45709</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46183</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45639</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45622</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>45181</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>46195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45693</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>44899</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45709</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46198</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45540</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45281</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45154</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46199</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45643</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45562</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45429</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45622</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46206</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46206</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46205</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45463</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>46205</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46205</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46207</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>46207</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46207</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>46206</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>46206</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46206</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>46162</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44546</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>46190</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45548</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45513</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>46258</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45009</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46260</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45548</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>46260</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45604</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>46260</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45641</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>46266</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45189</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>46267</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46269</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>46225</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46272</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>46230</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46029</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>46278</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>46281</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46281</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46280</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45518</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46238</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>46281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45747</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45699</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44966</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45334</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45621</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45699</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46287</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44966</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45463</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45321</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>46093</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>46287</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46244</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46288</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>46288</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>44543</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>46246</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45404</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45436</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45667</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45401</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46048</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46293</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46247</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>46290</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44817</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45890</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45539</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>46295</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46252</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45223</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46254</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45603</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45693</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46296</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>46296</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>46244</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45315</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45621</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46254</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46254</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46253</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45744</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45631</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45771</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>45268</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45208</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45548</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45169</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45153</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45611</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45107</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45076</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45429</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45593</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45692</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45693</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45782</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45785</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44741</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45485</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45482</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45607</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45756</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45800</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46030</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>46162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45211</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45834</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>46290</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45758</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45769</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>46177</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>46258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44496</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46009</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45807</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45170</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44966</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45588</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>46195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>46199</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45154</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45534</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45534</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>45602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>44658</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44717</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>44809</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>45581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45859</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44539</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45709</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>46187</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>46176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46142</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>46231</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45442</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44582</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44550</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44718</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44717</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44755</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44862</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44788</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44875</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44510</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44530</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44698</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44501</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44880</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45231</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45622</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44603</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44964</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45561</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44890</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45231</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45643</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44960</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45807</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>46009</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>46009</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45518</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45677</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>46013</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>46013</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45807</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>45715</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45463</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46029</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45807</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45793</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45793</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45793</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45371</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45909</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45820</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>46042</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45712</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>46048</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45323</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45377</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45811</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45443</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45460</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45702</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>46059</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45936</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45469</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45429</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45940</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45811</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45588</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45810</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>46076</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45180</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45947</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45363</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>46080</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46080</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45951</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45951</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45818</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45949</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>46084</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>46084</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>46084</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44543</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>46084</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>46084</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>46084</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45813</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45813</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45957</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45954</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45813</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45958</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46087</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>46087</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45813</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45813</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45097</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45005</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45372</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45964</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45771</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45075</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45463</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44930</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>46104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45141</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45819</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>46105</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45981</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45821</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45821</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45820</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45820</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>46112</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45820</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>46113</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45986</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45824</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45824</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45824</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44823</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45824</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>46120</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45988</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46120</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45992</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45826</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46121</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45428</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45238</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45826</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45996</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45999</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45999</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45999</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46001</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>46127</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>46127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46133</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>46132</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45251</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45831</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45671</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45835</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45189</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45834</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45834</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44659</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45835</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45189</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45838</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45837</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>45133</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45839</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45838</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45837</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45837</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45840</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45840</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44546</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45554</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44993</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>44502</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44595</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45315</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>44601</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45092</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45308</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>46139</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45321</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44830</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45463</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46140</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44648</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45909</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45818</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45869</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45440</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45594</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45869</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45471</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45471</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45870</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45870</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45873</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44950</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46148</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45379</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46148</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>46148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>46148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>46148</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>46148</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46148</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>46148</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45218</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45460</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44910</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45933</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45631</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44575</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46160</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46162</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46162</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>46163</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46164</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>46167</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46167</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45818</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45513</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46167</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45498</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45950</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>46167</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46167</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45308</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46168</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46170</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45882</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>44973</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45588</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45882</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45379</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45882</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45086</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>46177</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>46181</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46181</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45513</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>46183</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>46183</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45709</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46183</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45639</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45622</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>45181</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>46195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45693</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>44899</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45709</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46198</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45540</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45281</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45154</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46199</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45643</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45562</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45429</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45622</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46206</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46206</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46205</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45463</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>46205</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46205</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46207</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>46207</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46207</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>46206</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>46206</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46206</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>46162</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44546</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>46190</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45548</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45513</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>46258</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45009</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46260</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45548</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>46260</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45604</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>46260</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45641</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>46266</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45189</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>46267</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46269</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>46225</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46272</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>46230</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46029</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>46278</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>46281</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46281</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46280</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45518</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46238</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>46281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45747</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45699</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44966</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45334</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45621</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45699</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46287</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44966</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45463</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45321</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>46093</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>46287</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46244</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46288</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>46288</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>44543</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>46246</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45404</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45436</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45667</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45401</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46048</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46293</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46247</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>46290</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44817</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45890</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45539</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>46295</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46252</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45223</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46254</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45603</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45693</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46296</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>46296</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>46244</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45315</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45621</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46254</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46254</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46253</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45744</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45631</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45771</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>45268</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45208</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45548</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45169</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45153</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45611</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45107</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45076</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45429</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45593</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45692</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45693</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45782</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45785</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44741</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45485</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45482</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45607</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45756</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45800</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46030</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>46162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45211</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45834</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>46290</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45758</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>46258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44496</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44966</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45807</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>45602</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45849</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45170</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>46099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>46009</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46199</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46226</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>46302</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46262</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>45442</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44717</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>45805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45813</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45859</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>46187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46142</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>46231</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>46301</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44718</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44711</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44717</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44602</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44788</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44875</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44530</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44602</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44623</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>44698</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>44890</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45154</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45429</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45513</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45709</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44910</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45372</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45562</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45160</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45771</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45621</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45379</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45218</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45463</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>44797</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>44886</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45107</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44966</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45075</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44546</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45315</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>44547</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45463</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45086</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45321</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45189</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45610</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45667</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>45379</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45334</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>44938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44964</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>44964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45428</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45807</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45807</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45554</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45548</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>44899</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45831</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45404</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45436</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45460</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45820</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45911</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45460</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45782</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45539</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45429</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45009</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45133</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45917</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45518</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45518</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45922</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45540</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45070</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45141</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45513</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44543</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45793</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45513</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45622</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>45796</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44603</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45793</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45793</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44950</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45371</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45377</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45936</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45323</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45548</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45677</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45429</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45189</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45810</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45401</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45940</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45811</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45811</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45813</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45813</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45813</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45813</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45189</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45268</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45076</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45820</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45622</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45622</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45819</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45744</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45947</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45824</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45949</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45715</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45821</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45824</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45824</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45824</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45826</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45561</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45826</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45622</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45693</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45831</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45951</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45958</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45957</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45964</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45643</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45631</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45702</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45834</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45838</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45835</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45837</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45838</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45835</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45837</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44993</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45463</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45837</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45839</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45693</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45575</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45604</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45611</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45840</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45840</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45967</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45699</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45845</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45281</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45699</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45869</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45870</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45870</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45869</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45643</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45208</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45873</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45092</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45671</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44575</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45882</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45693</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45882</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45882</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45631</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45548</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45747</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45986</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45231</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45986</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44543</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46104</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>46105</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45471</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45471</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45988</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>46113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>46112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44820</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44823</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>46121</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45993</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46120</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45994</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>46120</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>44880</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45996</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45999</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45999</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>46127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>46127</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>46001</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>46002</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44830</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>46132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>46133</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>44960</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>46133</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46134</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45807</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45169</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45308</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45308</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46009</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46009</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>46013</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46013</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46013</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45363</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45603</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44834</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45498</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45909</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45440</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>44930</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>46029</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>46029</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>46029</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44502</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45747</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>46042</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45005</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>46042</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45712</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45639</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44659</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45818</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>44648</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>46139</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46140</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>46048</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>44601</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45594</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>44973</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>46055</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>46059</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>46148</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>46148</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>46148</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>46148</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46148</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>46148</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>46148</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46148</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>46148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>46153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>46076</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45933</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>45818</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>46080</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46080</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>46084</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>46084</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46084</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46087</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>46087</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>46160</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>46160</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>46162</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>46162</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>46162</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>46163</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>46164</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>45950</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46163</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45818</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>46167</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>46168</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46167</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46167</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46167</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46167</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46170</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>46177</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46177</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>46178</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46181</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46181</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>46183</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>46183</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>46183</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>46195</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>46196</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>46199</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>46205</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46207</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46207</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>46206</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>46206</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>46206</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>46206</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>46207</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>46190</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46162</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45641</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>46266</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>46225</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>46272</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>46269</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>46230</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>46029</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>46280</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46278</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>46281</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>46238</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45463</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>46093</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>46288</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46287</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46287</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>46244</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>46247</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>46290</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>46048</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>46246</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>46288</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>46293</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>45890</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46295</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>46252</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46296</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>46296</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>46244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>46297</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>46254</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>46253</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46254</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>46254</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46258</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>46301</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>46301</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>46301</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>46304</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>46303</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>46304</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>46260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>46260</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>46059</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>46260</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46260</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46304</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>44741</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>45485</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45482</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45607</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45756</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45800</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46030</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 36383-2024</t>
+          <t>A 23383-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45534</v>
+        <v>46162</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -997,51 +997,177 @@
           <t>ÖVERKALIX</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>42.1</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
       </c>
       <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Myskmåra
+Sparvuggla
+Tretåig hackspett
+Björksplintborre
+Nästlav
+Sotlav
+Trådticka
+Vågbandad barkbock
+Järpe
+Liljekonvalj
+Sälg
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/artfynd/A 23383-2026 artfynd.xlsx", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/kartor/A 23383-2026 karta.png", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/kartor_geotiff/A 23383-2026 georefererad karta.tif", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/knärot/A 23383-2026 karta knärot.png", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/klagomål/A 23383-2026 FSC-klagomål.docx", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/klagomålsmail/A 23383-2026 FSC-klagomål mail.docx", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/tillsyn/A 23383-2026 tillsynsbegäran.docx", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/tillsynsmail/A 23383-2026 tillsynsbegäran mail.docx", "A 23383-2026")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2513/fåglar/A 23383-2026 prioriterade fågelarter.docx", "A 23383-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 36383-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45534</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÖVERKALIX</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>7</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>8</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>13</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>39</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -1058,161 +1184,36 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/artfynd/A 36383-2024 artfynd.xlsx", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/kartor/A 36383-2024 karta.png", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/kartor_geotiff/A 36383-2024 georefererad karta.tif", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/klagomål/A 36383-2024 FSC-klagomål.docx", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/klagomålsmail/A 36383-2024 FSC-klagomål mail.docx", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/tillsyn/A 36383-2024 tillsynsbegäran.docx", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/tillsynsmail/A 36383-2024 tillsynsbegäran mail.docx", "A 36383-2024")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2513/fåglar/A 36383-2024 prioriterade fågelarter.docx", "A 36383-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 23383-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÖVERKALIX</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>13</v>
-      </c>
-      <c r="T6" t="n">
-        <v>26</v>
-      </c>
-      <c r="U6" t="n">
-        <v>26</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Myskmåra
-Tretåig hackspett
-Björksplintborre
-Nästlav
-Sotlav
-Trådticka
-Vågbandad barkbock
-Järpe
-Liljekonvalj
-Sälg
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/artfynd/A 23383-2026 artfynd.xlsx", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/kartor/A 23383-2026 karta.png", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/kartor_geotiff/A 23383-2026 georefererad karta.tif", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/knärot/A 23383-2026 karta knärot.png", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/klagomål/A 23383-2026 FSC-klagomål.docx", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/klagomålsmail/A 23383-2026 FSC-klagomål mail.docx", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/tillsyn/A 23383-2026 tillsynsbegäran.docx", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/tillsynsmail/A 23383-2026 tillsynsbegäran mail.docx", "A 23383-2026")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2513/fåglar/A 23383-2026 prioriterade fågelarter.docx", "A 23383-2026")</f>
         <v/>
       </c>
     </row>
@@ -1236,7 +1237,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1360,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1481,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1607,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1724,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1844,7 @@
         <v>45211</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1958,7 @@
         <v>45163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2072,7 @@
         <v>45834</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2180,7 +2181,7 @@
         <v>46290</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2294,7 +2295,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2407,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2523,7 +2524,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2641,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2752,7 +2753,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2864,7 +2865,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2981,7 @@
         <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3092,7 +3093,7 @@
         <v>45831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3208,7 +3209,7 @@
         <v>45758</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3324,7 +3325,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3436,7 +3437,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3548,7 +3549,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3660,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3771,7 +3772,7 @@
         <v>46258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3994,7 +3995,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4106,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4220,7 +4221,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4331,7 +4332,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4437,7 +4438,7 @@
         <v>44496</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4549,7 @@
         <v>44966</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4654,7 +4655,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4764,7 +4765,7 @@
         <v>45807</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4875,7 +4876,7 @@
         <v>45602</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4986,7 +4987,7 @@
         <v>45849</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5098,7 @@
         <v>45170</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5212,7 +5213,7 @@
         <v>46099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5318,7 +5319,7 @@
         <v>46009</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5429,7 +5430,7 @@
         <v>45588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5541,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5652,7 @@
         <v>46199</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5767,7 @@
         <v>46226</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5877,7 +5878,7 @@
         <v>46302</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5988,7 +5989,7 @@
         <v>46262</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6099,7 +6100,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6210,7 +6211,7 @@
         <v>44658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6315,7 +6316,7 @@
         <v>45442</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6425,7 +6426,7 @@
         <v>44717</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6535,7 @@
         <v>45805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6644,7 +6645,7 @@
         <v>45813</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6759,7 @@
         <v>45859</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6869,7 @@
         <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6978,7 +6979,7 @@
         <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7087,7 +7088,7 @@
         <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7196,7 +7197,7 @@
         <v>44539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7305,7 +7306,7 @@
         <v>45581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7419,7 +7420,7 @@
         <v>45581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7529,7 +7530,7 @@
         <v>46187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7643,7 +7644,7 @@
         <v>46142</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7753,7 +7754,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7863,7 +7864,7 @@
         <v>46231</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7973,7 +7974,7 @@
         <v>46301</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8083,7 +8084,7 @@
         <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8193,7 +8194,7 @@
         <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8307,7 +8308,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8380,7 +8381,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8453,7 +8454,7 @@
         <v>44718</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8526,7 +8527,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8599,7 +8600,7 @@
         <v>44711</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8677,7 +8678,7 @@
         <v>44717</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8750,7 +8751,7 @@
         <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8848,7 +8849,7 @@
         <v>44602</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8921,7 +8922,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8994,7 +8995,7 @@
         <v>44788</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9067,7 +9068,7 @@
         <v>44875</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9140,7 +9141,7 @@
         <v>44530</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9213,7 +9214,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9291,7 +9292,7 @@
         <v>44602</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9369,7 +9370,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9447,7 +9448,7 @@
         <v>44623</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9525,7 +9526,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9603,7 +9604,7 @@
         <v>45238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9676,7 +9677,7 @@
         <v>44698</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9749,7 +9750,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9822,7 +9823,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9895,7 +9896,7 @@
         <v>44890</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9973,7 +9974,7 @@
         <v>45154</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10046,7 +10047,7 @@
         <v>45692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10124,7 +10125,7 @@
         <v>45429</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10202,7 +10203,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10275,7 +10276,7 @@
         <v>45513</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10353,7 +10354,7 @@
         <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10426,7 +10427,7 @@
         <v>45709</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10499,7 +10500,7 @@
         <v>44910</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10572,7 +10573,7 @@
         <v>45372</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10645,7 +10646,7 @@
         <v>45562</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10718,7 +10719,7 @@
         <v>45160</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10796,7 +10797,7 @@
         <v>45771</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10874,7 +10875,7 @@
         <v>45621</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10947,7 +10948,7 @@
         <v>45379</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11020,7 +11021,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11098,7 +11099,7 @@
         <v>45593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11176,7 +11177,7 @@
         <v>45218</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11249,7 +11250,7 @@
         <v>45463</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11327,7 +11328,7 @@
         <v>44797</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11405,7 +11406,7 @@
         <v>44886</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11478,7 +11479,7 @@
         <v>45107</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11556,7 +11557,7 @@
         <v>44966</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11629,7 +11630,7 @@
         <v>45075</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11707,7 +11708,7 @@
         <v>44546</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11780,7 +11781,7 @@
         <v>45223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11853,7 +11854,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11926,7 +11927,7 @@
         <v>45315</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11999,7 +12000,7 @@
         <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12077,7 +12078,7 @@
         <v>44547</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12150,7 +12151,7 @@
         <v>44546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12223,7 +12224,7 @@
         <v>45463</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12301,7 +12302,7 @@
         <v>45086</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12374,7 +12375,7 @@
         <v>45321</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12447,7 +12448,7 @@
         <v>45244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12520,7 +12521,7 @@
         <v>45189</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12593,7 +12594,7 @@
         <v>45610</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12671,7 +12672,7 @@
         <v>45667</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12744,7 +12745,7 @@
         <v>45379</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12822,7 +12823,7 @@
         <v>45334</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12895,7 +12896,7 @@
         <v>44938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12973,7 +12974,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13051,7 +13052,7 @@
         <v>44964</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13124,7 +13125,7 @@
         <v>44964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13197,7 +13198,7 @@
         <v>45428</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13275,7 +13276,7 @@
         <v>45807</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13353,7 +13354,7 @@
         <v>45807</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13431,7 +13432,7 @@
         <v>45554</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13504,7 +13505,7 @@
         <v>45548</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13582,7 +13583,7 @@
         <v>45469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13655,7 +13656,7 @@
         <v>45904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13728,7 +13729,7 @@
         <v>44899</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13801,7 +13802,7 @@
         <v>45831</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13874,7 +13875,7 @@
         <v>45404</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13947,7 +13948,7 @@
         <v>45436</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14025,7 +14026,7 @@
         <v>45460</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14098,7 +14099,7 @@
         <v>45820</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14176,7 +14177,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14249,7 +14250,7 @@
         <v>45911</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14327,7 +14328,7 @@
         <v>45460</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14400,7 +14401,7 @@
         <v>45782</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14478,7 +14479,7 @@
         <v>45539</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14556,7 +14557,7 @@
         <v>45429</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14634,7 +14635,7 @@
         <v>45009</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14707,7 +14708,7 @@
         <v>45133</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14780,7 +14781,7 @@
         <v>45785</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14853,7 +14854,7 @@
         <v>45771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14931,7 +14932,7 @@
         <v>45917</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15004,7 +15005,7 @@
         <v>45518</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15082,7 +15083,7 @@
         <v>45518</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15160,7 +15161,7 @@
         <v>45922</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15238,7 +15239,7 @@
         <v>45588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15311,7 +15312,7 @@
         <v>45540</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15384,7 +15385,7 @@
         <v>45070</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15462,7 +15463,7 @@
         <v>45141</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15535,7 +15536,7 @@
         <v>45513</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15613,7 +15614,7 @@
         <v>44543</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15686,7 +15687,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15764,7 +15765,7 @@
         <v>45793</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15842,7 +15843,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15915,7 +15916,7 @@
         <v>45513</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15993,7 +15994,7 @@
         <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16071,7 +16072,7 @@
         <v>45622</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16144,7 +16145,7 @@
         <v>45796</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16222,7 +16223,7 @@
         <v>44603</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16300,7 +16301,7 @@
         <v>45793</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16378,7 +16379,7 @@
         <v>45793</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16456,7 +16457,7 @@
         <v>44950</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16534,7 +16535,7 @@
         <v>45371</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16607,7 +16608,7 @@
         <v>45588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16680,7 +16681,7 @@
         <v>45377</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16753,7 +16754,7 @@
         <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16826,7 +16827,7 @@
         <v>45936</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16904,7 +16905,7 @@
         <v>45323</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16977,7 +16978,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17055,7 +17056,7 @@
         <v>45548</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17133,7 +17134,7 @@
         <v>45677</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17206,7 +17207,7 @@
         <v>45429</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17284,7 +17285,7 @@
         <v>45189</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17357,7 +17358,7 @@
         <v>45810</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17435,7 +17436,7 @@
         <v>45401</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17508,7 +17509,7 @@
         <v>45097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17586,7 +17587,7 @@
         <v>45940</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17664,7 +17665,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17742,7 +17743,7 @@
         <v>45811</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17815,7 +17816,7 @@
         <v>45811</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17888,7 +17889,7 @@
         <v>45813</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17966,7 +17967,7 @@
         <v>45813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18039,7 +18040,7 @@
         <v>45813</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18117,7 +18118,7 @@
         <v>45813</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18195,7 +18196,7 @@
         <v>45813</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18273,7 +18274,7 @@
         <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18351,7 +18352,7 @@
         <v>45813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18429,7 +18430,7 @@
         <v>45189</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18502,7 +18503,7 @@
         <v>45946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18580,7 +18581,7 @@
         <v>45268</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18658,7 +18659,7 @@
         <v>45820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18736,7 +18737,7 @@
         <v>45076</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18814,7 +18815,7 @@
         <v>45820</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18892,7 +18893,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18970,7 +18971,7 @@
         <v>45622</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19043,7 +19044,7 @@
         <v>45622</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19116,7 +19117,7 @@
         <v>45819</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19194,7 +19195,7 @@
         <v>45744</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19267,7 +19268,7 @@
         <v>45820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19345,7 +19346,7 @@
         <v>45947</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19423,7 +19424,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19501,7 +19502,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19579,7 +19580,7 @@
         <v>45824</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19657,7 +19658,7 @@
         <v>45949</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19735,7 +19736,7 @@
         <v>45715</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19808,7 +19809,7 @@
         <v>45821</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19881,7 +19882,7 @@
         <v>45824</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19959,7 +19960,7 @@
         <v>45621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20032,7 +20033,7 @@
         <v>45824</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20110,7 +20111,7 @@
         <v>45824</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20188,7 +20189,7 @@
         <v>45826</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20266,7 +20267,7 @@
         <v>45561</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20344,7 +20345,7 @@
         <v>45826</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20417,7 +20418,7 @@
         <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20490,7 +20491,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20568,7 +20569,7 @@
         <v>45622</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20641,7 +20642,7 @@
         <v>45951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20719,7 +20720,7 @@
         <v>45693</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20797,7 +20798,7 @@
         <v>45831</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20870,7 +20871,7 @@
         <v>45951</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20943,7 +20944,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21021,7 +21022,7 @@
         <v>45958</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21099,7 +21100,7 @@
         <v>45957</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21177,7 +21178,7 @@
         <v>45964</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21255,7 +21256,7 @@
         <v>45834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21333,7 +21334,7 @@
         <v>45643</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21406,7 +21407,7 @@
         <v>45631</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21479,7 +21480,7 @@
         <v>45702</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21552,7 +21553,7 @@
         <v>45834</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21625,7 +21626,7 @@
         <v>45838</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21703,7 +21704,7 @@
         <v>45835</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21781,7 +21782,7 @@
         <v>45251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21859,7 +21860,7 @@
         <v>45837</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21932,7 +21933,7 @@
         <v>45838</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22005,7 +22006,7 @@
         <v>45835</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22083,7 +22084,7 @@
         <v>45837</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22156,7 +22157,7 @@
         <v>44993</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22229,7 +22230,7 @@
         <v>45463</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22307,7 +22308,7 @@
         <v>45837</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22380,7 +22381,7 @@
         <v>45839</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22458,7 +22459,7 @@
         <v>45693</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22536,7 +22537,7 @@
         <v>45575</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22614,7 +22615,7 @@
         <v>45604</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22687,7 +22688,7 @@
         <v>45611</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22765,7 +22766,7 @@
         <v>45840</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22843,7 +22844,7 @@
         <v>45840</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22921,7 +22922,7 @@
         <v>45181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22994,7 +22995,7 @@
         <v>45967</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23072,7 +23073,7 @@
         <v>45699</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23150,7 +23151,7 @@
         <v>45845</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23223,7 +23224,7 @@
         <v>45281</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23301,7 +23302,7 @@
         <v>45699</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23379,7 +23380,7 @@
         <v>45869</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23452,7 +23453,7 @@
         <v>45870</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23530,7 +23531,7 @@
         <v>45870</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23608,7 +23609,7 @@
         <v>45869</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23686,7 +23687,7 @@
         <v>45643</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23759,7 +23760,7 @@
         <v>45208</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23837,7 +23838,7 @@
         <v>45873</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23910,7 +23911,7 @@
         <v>45092</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23988,7 +23989,7 @@
         <v>45671</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24061,7 +24062,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24139,7 +24140,7 @@
         <v>45882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24212,7 +24213,7 @@
         <v>44575</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24285,7 +24286,7 @@
         <v>45882</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24358,7 +24359,7 @@
         <v>45693</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24436,7 +24437,7 @@
         <v>45882</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24514,7 +24515,7 @@
         <v>45882</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24592,7 +24593,7 @@
         <v>45631</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24665,7 +24666,7 @@
         <v>45548</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24743,7 +24744,7 @@
         <v>45747</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24816,7 +24817,7 @@
         <v>45986</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24889,7 +24890,7 @@
         <v>45231</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24962,7 +24963,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25035,7 +25036,7 @@
         <v>45986</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25108,7 +25109,7 @@
         <v>44543</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25181,7 +25182,7 @@
         <v>46104</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25254,7 +25255,7 @@
         <v>46105</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25332,7 +25333,7 @@
         <v>45471</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25410,7 +25411,7 @@
         <v>45471</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25488,7 +25489,7 @@
         <v>45988</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25561,7 +25562,7 @@
         <v>46113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25639,7 +25640,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25717,7 +25718,7 @@
         <v>46112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25790,7 +25791,7 @@
         <v>44820</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25868,7 +25869,7 @@
         <v>44823</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25946,7 +25947,7 @@
         <v>46121</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26024,7 +26025,7 @@
         <v>45993</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26102,7 +26103,7 @@
         <v>46120</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26180,7 +26181,7 @@
         <v>45994</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26253,7 +26254,7 @@
         <v>46120</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26331,7 +26332,7 @@
         <v>44880</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26404,7 +26405,7 @@
         <v>45996</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26477,7 +26478,7 @@
         <v>45999</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26550,7 +26551,7 @@
         <v>45999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26623,7 +26624,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26696,7 +26697,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26769,7 +26770,7 @@
         <v>45999</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26842,7 +26843,7 @@
         <v>46127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26920,7 +26921,7 @@
         <v>46127</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26998,7 +26999,7 @@
         <v>46001</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27076,7 +27077,7 @@
         <v>46002</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27154,7 +27155,7 @@
         <v>44830</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27227,7 +27228,7 @@
         <v>46132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27305,7 +27306,7 @@
         <v>46133</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27383,7 +27384,7 @@
         <v>44960</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27461,7 +27462,7 @@
         <v>46133</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27534,7 +27535,7 @@
         <v>46134</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27612,7 +27613,7 @@
         <v>45807</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27690,7 +27691,7 @@
         <v>45169</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27763,7 +27764,7 @@
         <v>45308</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27836,7 +27837,7 @@
         <v>45308</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27909,7 +27910,7 @@
         <v>46009</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27987,7 +27988,7 @@
         <v>46009</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28060,7 +28061,7 @@
         <v>46013</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28133,7 +28134,7 @@
         <v>46013</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28206,7 +28207,7 @@
         <v>46013</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28279,7 +28280,7 @@
         <v>45363</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28352,7 +28353,7 @@
         <v>45603</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28430,7 +28431,7 @@
         <v>44834</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28503,7 +28504,7 @@
         <v>45498</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28576,7 +28577,7 @@
         <v>45909</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28649,7 +28650,7 @@
         <v>45440</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28727,7 +28728,7 @@
         <v>44930</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28800,7 +28801,7 @@
         <v>46029</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28873,7 +28874,7 @@
         <v>46029</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28946,7 +28947,7 @@
         <v>46029</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29019,7 +29020,7 @@
         <v>44502</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29092,7 +29093,7 @@
         <v>45747</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29165,7 +29166,7 @@
         <v>46042</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29238,7 +29239,7 @@
         <v>45005</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29311,7 +29312,7 @@
         <v>46042</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29384,7 +29385,7 @@
         <v>45153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29457,7 +29458,7 @@
         <v>45712</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29530,7 +29531,7 @@
         <v>45639</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29603,7 +29604,7 @@
         <v>44659</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29676,7 +29677,7 @@
         <v>45818</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29749,7 +29750,7 @@
         <v>44648</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29822,7 +29823,7 @@
         <v>46139</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29900,7 +29901,7 @@
         <v>46140</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29978,7 +29979,7 @@
         <v>46048</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30051,7 +30052,7 @@
         <v>44601</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30129,7 +30130,7 @@
         <v>45594</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30207,7 +30208,7 @@
         <v>44973</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30285,7 +30286,7 @@
         <v>46055</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30358,7 +30359,7 @@
         <v>46059</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30436,7 +30437,7 @@
         <v>46148</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30514,7 +30515,7 @@
         <v>46148</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30592,7 +30593,7 @@
         <v>46148</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30670,7 +30671,7 @@
         <v>46148</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30748,7 +30749,7 @@
         <v>46148</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30826,7 +30827,7 @@
         <v>46148</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30904,7 +30905,7 @@
         <v>46148</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30982,7 +30983,7 @@
         <v>46148</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31060,7 +31061,7 @@
         <v>46148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31138,7 +31139,7 @@
         <v>46153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31216,7 +31217,7 @@
         <v>46076</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31289,7 +31290,7 @@
         <v>45933</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31367,7 +31368,7 @@
         <v>45818</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31440,7 +31441,7 @@
         <v>46080</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31513,7 +31514,7 @@
         <v>46080</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31586,7 +31587,7 @@
         <v>46084</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31659,7 +31660,7 @@
         <v>46084</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31732,7 +31733,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31805,7 +31806,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31878,7 +31879,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31951,7 +31952,7 @@
         <v>46084</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32024,7 +32025,7 @@
         <v>46087</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32102,7 +32103,7 @@
         <v>46087</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32180,7 +32181,7 @@
         <v>46160</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32258,7 +32259,7 @@
         <v>46160</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32336,7 +32337,7 @@
         <v>46162</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32409,7 +32410,7 @@
         <v>46162</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32482,7 +32483,7 @@
         <v>46162</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32555,7 +32556,7 @@
         <v>46163</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32633,7 +32634,7 @@
         <v>46164</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32711,7 +32712,7 @@
         <v>45950</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32784,7 +32785,7 @@
         <v>46163</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32857,7 +32858,7 @@
         <v>45818</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32930,7 +32931,7 @@
         <v>46167</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33008,7 +33009,7 @@
         <v>46168</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33086,7 +33087,7 @@
         <v>46167</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33164,7 +33165,7 @@
         <v>46167</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33242,7 +33243,7 @@
         <v>46167</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33320,7 +33321,7 @@
         <v>46167</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33398,7 +33399,7 @@
         <v>46170</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33476,7 +33477,7 @@
         <v>45944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33549,7 +33550,7 @@
         <v>46177</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33627,7 +33628,7 @@
         <v>46177</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33705,7 +33706,7 @@
         <v>46178</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33778,7 +33779,7 @@
         <v>46181</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33856,7 +33857,7 @@
         <v>46181</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33934,7 +33935,7 @@
         <v>46183</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34012,7 +34013,7 @@
         <v>46183</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34090,7 +34091,7 @@
         <v>46183</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34168,7 +34169,7 @@
         <v>46195</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34246,7 +34247,7 @@
         <v>46196</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34324,7 +34325,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34402,7 +34403,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34480,7 +34481,7 @@
         <v>46199</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34558,7 +34559,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34631,7 +34632,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34704,7 +34705,7 @@
         <v>46205</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34777,7 +34778,7 @@
         <v>46207</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34850,7 +34851,7 @@
         <v>46207</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34923,7 +34924,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35001,7 +35002,7 @@
         <v>46206</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35079,7 +35080,7 @@
         <v>46206</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35152,7 +35153,7 @@
         <v>46206</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35230,7 +35231,7 @@
         <v>46206</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35303,7 +35304,7 @@
         <v>46207</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35376,7 +35377,7 @@
         <v>46190</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35454,7 +35455,7 @@
         <v>46162</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35532,7 +35533,7 @@
         <v>45641</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35605,7 +35606,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35678,7 +35679,7 @@
         <v>46266</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35751,7 +35752,7 @@
         <v>46225</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35824,7 +35825,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35902,7 +35903,7 @@
         <v>46272</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35980,7 +35981,7 @@
         <v>46269</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36053,7 +36054,7 @@
         <v>46230</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36131,7 +36132,7 @@
         <v>46029</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36204,7 +36205,7 @@
         <v>46280</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36282,7 +36283,7 @@
         <v>46278</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36355,7 +36356,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36433,7 +36434,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36511,7 +36512,7 @@
         <v>46281</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36589,7 +36590,7 @@
         <v>46238</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36667,7 +36668,7 @@
         <v>45463</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36745,7 +36746,7 @@
         <v>46093</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36818,7 +36819,7 @@
         <v>46288</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36896,7 +36897,7 @@
         <v>46287</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36969,7 +36970,7 @@
         <v>46287</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37042,7 +37043,7 @@
         <v>46244</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37120,7 +37121,7 @@
         <v>46247</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37193,7 +37194,7 @@
         <v>46290</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37266,7 +37267,7 @@
         <v>46048</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37339,7 +37340,7 @@
         <v>46246</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37417,7 +37418,7 @@
         <v>46288</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37490,7 +37491,7 @@
         <v>46293</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37563,7 +37564,7 @@
         <v>45890</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37641,7 +37642,7 @@
         <v>46295</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37719,7 +37720,7 @@
         <v>46252</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37797,7 +37798,7 @@
         <v>46296</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37875,7 +37876,7 @@
         <v>46296</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37953,7 +37954,7 @@
         <v>46244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38031,7 +38032,7 @@
         <v>46297</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38109,7 +38110,7 @@
         <v>46254</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38187,7 +38188,7 @@
         <v>46253</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38265,7 +38266,7 @@
         <v>46254</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38343,7 +38344,7 @@
         <v>46254</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38421,7 +38422,7 @@
         <v>46258</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38499,7 +38500,7 @@
         <v>46301</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38577,7 +38578,7 @@
         <v>46301</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38655,7 +38656,7 @@
         <v>46301</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38733,7 +38734,7 @@
         <v>46304</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38811,7 +38812,7 @@
         <v>46303</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38889,7 +38890,7 @@
         <v>46304</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38967,7 +38968,7 @@
         <v>46260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39040,7 +39041,7 @@
         <v>46260</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39118,7 +39119,7 @@
         <v>46059</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39196,7 +39197,7 @@
         <v>46260</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39274,7 +39275,7 @@
         <v>46260</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39352,7 +39353,7 @@
         <v>46304</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39425,7 +39426,7 @@
         <v>44741</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39498,7 +39499,7 @@
         <v>45485</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39576,7 +39577,7 @@
         <v>45482</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39654,7 +39655,7 @@
         <v>45607</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39732,7 +39733,7 @@
         <v>45756</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39805,7 +39806,7 @@
         <v>45800</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39883,7 +39884,7 @@
         <v>46030</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46162</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45534</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45211</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45834</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45758</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45908</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45908</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>46177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45894</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45588</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>46099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46195</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46199</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45534</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45534</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>46226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>46302</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46262</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45807</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45849</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44717</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44809</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>46187</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>46176</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45442</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>46231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45859</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44718</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44711</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44717</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44602</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44788</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45622</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44603</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45561</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45231</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>45643</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44960</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45518</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45677</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45715</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45371</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45702</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45443</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45460</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44886</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45469</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45429</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44543</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>45097</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45005</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45771</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45372</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45075</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45160</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45086</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45807</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44964</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45807</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45818</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45440</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45831</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45133</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45820</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45911</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44546</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45922</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45554</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>46148</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>46148</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44502</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>46148</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>46148</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>46148</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>46148</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46148</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46148</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45070</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>46148</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44595</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>46153</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45936</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45315</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44601</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45092</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45940</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45308</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45946</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45321</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45947</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45947</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45463</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45951</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45949</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45957</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45954</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45933</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45958</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44547</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>46160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46160</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45471</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45471</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>46162</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>46163</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44950</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>46162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45379</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>46163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45218</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>46164</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>46167</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>46167</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44910</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46167</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46167</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45631</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>44820</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44575</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45988</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45993</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45996</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44797</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45999</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45513</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>46001</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45498</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>46170</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>46002</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45308</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45807</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>46009</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>46009</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45588</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45379</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45944</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>46013</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46013</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45513</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>46029</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46029</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>46029</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45709</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>46177</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45747</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45639</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46177</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46042</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46178</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>46042</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45712</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45622</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46048</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>46181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46181</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45181</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46055</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45693</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>46183</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46183</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46059</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44899</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45709</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45540</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>46183</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45643</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45562</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45429</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45622</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>46076</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46080</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>46080</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45818</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>46084</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>46084</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>46084</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45463</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>46084</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>46084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>46087</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46087</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44546</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45548</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45513</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>46195</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46104</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45548</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46196</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45604</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>46105</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44938</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46112</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>46113</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46198</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>46198</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46199</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>46120</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>46120</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45189</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46121</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46127</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46133</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46132</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46133</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46134</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>44659</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45518</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>46206</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45699</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>44966</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>46205</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>46207</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46207</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>46207</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45334</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45621</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>46190</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45699</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45321</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45107</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44543</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45641</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45404</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>46225</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46272</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45436</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>46230</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45667</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45401</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46029</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46278</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>46281</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45539</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>46281</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>46280</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45223</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>45603</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>45693</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45315</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45621</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46287</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45463</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>46093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46287</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45631</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45771</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45268</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>46244</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45208</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45548</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45169</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46288</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>46288</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>46246</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45611</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>45076</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>46048</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>46293</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45429</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45593</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46247</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45692</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46290</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45890</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46295</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46252</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45693</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>46296</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46296</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46244</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>46297</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>46254</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>46254</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46253</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46301</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>46301</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46301</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45785</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46303</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>46260</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46260</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46260</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45793</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45793</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45793</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46304</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45796</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46059</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46307</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45796</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45323</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46304</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46304</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45803</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45377</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>46266</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>46309</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>46308</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45811</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45810</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45813</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45813</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45813</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45813</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45813</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45813</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45813</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46267</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45819</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46269</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45821</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45821</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45820</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45820</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45820</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45820</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>46310</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45825</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45824</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45824</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45824</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45824</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45826</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45826</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45831</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45835</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45834</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45834</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45835</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45838</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45837</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45839</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45838</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45837</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45837</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45840</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45840</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45845</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45869</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45869</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45870</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45870</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45873</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45882</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45882</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45882</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45882</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44741</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45485</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45482</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45607</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45756</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45800</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>46030</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46162</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45534</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45211</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45834</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45758</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45908</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45908</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>46177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45894</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45588</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>46099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46195</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46199</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45534</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45534</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>46226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>46302</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46262</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45807</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45849</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44717</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44809</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>46187</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>46176</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45442</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>46231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45859</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44718</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44711</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44717</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44602</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44788</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45622</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44603</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45561</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45231</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>45643</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44960</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45518</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45677</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45715</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45371</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45702</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45443</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45460</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44886</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45469</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45429</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44543</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>45097</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45005</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45771</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45372</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45075</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45160</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45086</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45807</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44964</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45807</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45818</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45440</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45831</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45133</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45820</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45911</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44546</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45922</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45554</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>46148</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>46148</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44502</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>46148</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>46148</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>46148</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>46148</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46148</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>46148</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45070</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>46148</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44595</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>46153</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45936</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45315</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44601</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45092</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45940</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45308</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45946</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45321</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45947</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45947</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45463</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45951</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45949</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45957</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45954</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45933</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45958</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44547</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>46160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46160</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45471</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45471</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>46162</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>46163</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44950</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>46162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45379</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>46163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45218</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>46164</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>46167</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>46167</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44910</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46167</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46167</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45631</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>44820</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44575</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45988</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45993</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45996</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44797</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45999</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45513</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>46001</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45498</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>46170</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>46002</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45308</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45807</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>46009</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>46009</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45588</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45379</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45944</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>46013</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46013</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45513</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>46029</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46029</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>46029</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45709</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>46177</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45747</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45639</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46177</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46042</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46178</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>46042</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45712</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45622</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46048</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>46181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46181</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45181</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46055</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45693</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>46183</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46183</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46059</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44899</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45709</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45540</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>46183</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45643</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45562</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45429</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45622</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>46076</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46080</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>46080</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45818</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>46084</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>46084</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>46084</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45463</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>46084</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>46084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>46087</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46087</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44546</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45548</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45513</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>46195</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46104</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45548</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46196</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45604</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>46105</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44938</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46112</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>46113</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46198</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>46198</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46199</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>46120</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>46120</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45189</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46121</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46127</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46133</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46132</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46133</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46134</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>44659</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45518</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>46206</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45699</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>44966</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>46205</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>46207</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46207</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>46207</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45334</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45621</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>46190</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45699</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45321</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45107</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44543</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45641</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45404</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>46225</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46272</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45436</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>46230</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45667</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45401</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46029</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46278</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>46281</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45539</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>46281</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>46280</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45223</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>45603</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>45693</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45315</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45621</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46287</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45463</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>46093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46287</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45631</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45771</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45268</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>46244</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45208</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45548</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45169</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46288</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>46288</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>46246</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45611</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45107</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>45076</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>46048</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>46293</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45429</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45593</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46247</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45692</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46290</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45890</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46295</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46252</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45693</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>46296</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46296</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46244</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>46297</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>46254</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>46254</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46253</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46301</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>46301</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46301</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45785</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46303</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>46260</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46260</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46260</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45793</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45793</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45793</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46304</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45796</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46059</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46307</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45796</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45323</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46304</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46304</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45803</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45377</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>46266</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>46309</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>46308</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45811</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45810</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45813</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45813</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45813</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45813</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45813</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45813</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45813</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46267</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45819</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46269</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45821</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45821</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45820</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45820</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45820</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45820</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>46310</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45825</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45824</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45824</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45824</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45824</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45826</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45826</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45831</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45835</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45834</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45834</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45835</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45838</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45837</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45839</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45838</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45837</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45837</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45840</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45840</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45845</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45869</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45869</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45870</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45870</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45873</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45882</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45882</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45882</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45882</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44741</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45485</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45482</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45607</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45756</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45800</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>46030</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46162</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45534</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45211</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45834</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46177</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>46177</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>44645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>46199</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>46258</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45769</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45894</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45534</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>46195</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>46199</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46226</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46302</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44966</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>45154</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>45581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>46187</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>46142</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>46176</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45813</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46301</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44539</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44717</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45709</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44718</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44717</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44755</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44602</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44788</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45709</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45771</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45807</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45169</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45308</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45086</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45308</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45807</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>45238</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45363</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45231</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45603</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44834</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45498</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>44930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>45820</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46162</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45911</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>46163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>46164</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45917</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44502</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45950</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>46163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45818</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>46167</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45922</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>46167</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46167</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46167</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45005</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45153</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45639</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46170</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45429</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44601</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44973</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45940</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45154</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45372</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>46177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>46177</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45379</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45443</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44797</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45513</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44886</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45107</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45075</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44546</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45946</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44910</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45947</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45947</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45949</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>46181</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45160</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45951</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45951</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45954</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46183</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45958</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45621</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45957</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45218</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45223</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45180</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45315</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46196</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45321</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46198</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>46199</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45610</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45667</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>46205</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45986</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45463</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45986</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44964</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46207</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46207</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46206</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>46206</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>46206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46206</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45554</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46206</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46207</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>44546</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46190</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44823</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45463</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45993</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45548</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45996</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45999</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45999</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45999</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45641</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>46001</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>46002</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>46225</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45782</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45807</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>46230</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>46029</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>46280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45244</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>46278</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>46009</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45785</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>46009</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>46013</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>46013</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>46013</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>46281</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>46281</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>46281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>46238</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>46029</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46029</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>46029</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45793</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45463</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45796</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45747</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>46093</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45796</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46042</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>46042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45712</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45793</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45793</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>46288</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>46287</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>46287</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45377</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45323</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45803</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>46247</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>46290</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45810</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>46246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>46288</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46059</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45811</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45811</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45813</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45813</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45813</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45813</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45813</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>46293</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45820</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45820</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45820</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45819</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>46076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45820</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45821</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45821</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45824</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45890</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45824</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45824</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45826</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45826</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>46295</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45825</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45818</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46252</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>46296</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46296</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>46080</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>46080</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>46084</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>46084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46084</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45834</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>46087</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>46087</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>46244</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45838</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45835</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45837</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45838</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45835</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45837</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45837</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45839</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46297</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45840</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>46254</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45334</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>44938</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45840</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45845</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>46254</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46254</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45428</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46104</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>46105</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>46258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>46301</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>46301</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>46301</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46112</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>46304</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46303</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46121</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45869</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46120</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45870</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45870</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46304</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45869</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>46120</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>46260</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>46260</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46059</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>46260</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45873</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46260</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46127</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46127</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46304</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>46132</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45882</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46307</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45882</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45882</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>46133</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>44899</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>46308</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45436</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>46133</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>46134</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45460</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45539</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>46310</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>46266</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45518</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45518</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>46266</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46269</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45909</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45440</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>46314</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45513</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46314</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46316</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44659</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46316</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>46316</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45818</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46272</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>44648</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46139</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>46140</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46318</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44950</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46318</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46318</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46318</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45371</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45588</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45548</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>46148</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46148</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>46148</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>46148</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>46148</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>46148</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46148</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45429</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>46153</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45401</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45933</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45107</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>46160</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45076</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>46160</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45744</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45622</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45643</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45575</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45604</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45611</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45699</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45699</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45643</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45208</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45671</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45747</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>44890</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45315</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45562</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44966</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44547</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45189</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45379</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45469</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45404</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45460</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>45429</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45009</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45133</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45771</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45588</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45540</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45070</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45141</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>44543</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>44595</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45513</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45622</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44603</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45321</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45677</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45097</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45189</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45622</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45622</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45715</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45621</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45561</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45709</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>45693</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45702</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45251</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45463</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45693</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45181</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45092</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44575</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45693</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45631</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45548</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45231</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>44543</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45471</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45471</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44880</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>44830</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>44960</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>44741</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>45485</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>45482</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45607</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45756</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45800</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>46030</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>

--- a/Översikt ÖVERKALIX.xlsx
+++ b/Översikt ÖVERKALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46010</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45909</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46162</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45534</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>46162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>44943</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45544</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45211</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45834</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44960</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45908</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46177</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>46177</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>44645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>46199</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>46258</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45769</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45894</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45534</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45904</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>46195</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>46199</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46226</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44496</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46302</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44966</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>45154</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>45581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>45442</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>46187</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>46142</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>46176</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45813</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46301</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44539</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44717</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45709</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45394</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44718</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44717</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44755</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44602</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44788</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45709</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45771</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45807</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45169</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45308</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45086</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45308</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45807</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>45238</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45363</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45231</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45603</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44834</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45498</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>44930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>45820</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>45909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46162</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45911</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>46163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>46164</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45917</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44502</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45950</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>46163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45818</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>46167</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45922</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>46167</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46167</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46167</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45005</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45153</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45639</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46170</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45429</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44601</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44973</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45940</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45154</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45372</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>46177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>46177</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45379</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45443</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44797</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45513</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44886</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45107</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45075</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44546</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45946</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44910</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45947</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45947</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45949</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>46181</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45160</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45951</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45951</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45954</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46183</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45958</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45621</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45957</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45218</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45223</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45180</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45315</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46196</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45321</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46198</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>46199</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45610</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45667</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>46205</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45986</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45463</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45986</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44964</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46207</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46207</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46206</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>46206</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>46206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46206</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45554</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46206</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46207</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>44546</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46190</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44823</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45463</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45993</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45548</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45996</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45999</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45999</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45999</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45641</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>46001</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>46002</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>46225</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45782</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45807</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>46230</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>46029</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>46280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45244</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>46278</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>46009</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45785</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>46009</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>46013</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>46013</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>46013</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>46281</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>46281</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>46281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>46238</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>46029</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46029</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>46029</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45793</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45463</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45796</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45747</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>46093</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45796</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46042</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>46042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45712</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45793</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45793</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>46288</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>46287</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>46287</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45377</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45323</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45803</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>46247</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>46290</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45810</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>46246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>46288</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46059</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45811</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45811</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45813</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45813</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45813</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45813</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45813</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>46293</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45820</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45820</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45820</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45819</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>46076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45820</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45821</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45821</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45824</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45890</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45824</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45824</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45826</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45826</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>46295</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45825</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45818</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46252</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>46296</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46296</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>46080</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>46080</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>46084</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>46084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46084</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45834</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>46087</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>46087</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>46244</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45838</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45835</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45837</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45838</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45835</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45837</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45837</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45839</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46297</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45840</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>46254</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45334</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>44938</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45840</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45845</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>46254</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46254</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45428</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46104</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>46105</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>46258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>46301</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>46301</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>46301</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46112</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>46304</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46303</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46121</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45869</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46120</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45870</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45870</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46304</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45869</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>46120</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>46260</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>46260</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46059</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>46260</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45873</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46260</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46127</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46127</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46304</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>46132</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45882</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46307</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45882</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45882</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>46133</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>44899</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>46308</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45436</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>46133</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>46134</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45460</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45539</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>46310</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>46266</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45518</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45518</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>46266</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46269</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45909</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45440</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>46314</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45513</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46314</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46316</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44659</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46316</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>46316</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45818</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46272</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>44648</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46139</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>46140</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46318</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44950</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46318</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46318</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46318</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45371</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45588</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45548</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>46148</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46148</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>46148</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>46148</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>46148</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>46148</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46148</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45429</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>46153</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45401</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45933</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45107</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>46160</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45076</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>46160</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45744</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45622</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45643</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45575</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45604</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45611</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45699</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45699</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45643</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45208</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45671</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45747</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>44890</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45315</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45562</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44966</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44547</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45189</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45379</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45469</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45404</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45460</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>45429</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45009</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45133</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45771</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45588</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45540</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45070</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45141</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>44543</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>44595</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45513</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45622</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>44603</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45321</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45677</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45097</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45189</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45622</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45622</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45715</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45621</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45561</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45709</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>45693</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45702</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45251</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45463</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45693</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45181</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45092</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44575</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45693</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45631</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45548</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45231</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>44543</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45471</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45471</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44880</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>44830</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>44960</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>44741</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>45485</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>45482</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45607</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45756</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45800</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>46030</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
